--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
@@ -67,7 +67,7 @@
     <t>{.statusName}</t>
   </si>
   <si>
-    <t>{.allocatedMonth}</t>
+    <t>{.allocatedMonthStr}</t>
   </si>
   <si>
     <t>{.companyName}</t>
@@ -82,10 +82,10 @@
     <t>{.productCost}</t>
   </si>
   <si>
-    <t>{.initTransitCost}</t>
-  </si>
-  <si>
-    <t>{.initTransitTariff}</t>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
   <si>
     <t>{.currency}</t>
@@ -1050,7 +1050,7 @@
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
     <col min="6" max="6" width="24.125" customWidth="1"/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>单据编号</t>
   </si>
@@ -1045,7 +1045,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1057,10 +1057,10 @@
     <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.375" customWidth="1"/>
     <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="10" max="12" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1091,8 +1091,14 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1122,6 +1128,12 @@
       </c>
       <c r="J2" t="s">
         <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>单据编号</t>
   </si>
@@ -58,9 +58,6 @@
     <t>创建时间</t>
   </si>
   <si>
-    <t>币种（默认CNY）</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -79,16 +76,13 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.productCost}</t>
+    <t>{.currencySymbol}{.productCost}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>{.currency}</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1039,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1057,10 +1051,9 @@
     <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.375" customWidth="1"/>
     <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="12" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1088,52 +1081,34 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostExport.xlsx
@@ -76,7 +76,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.currencySymbol}{.productCost}</t>
+    <t>{.productCostStr}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1047,8 +1047,8 @@
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="24.125" customWidth="1"/>
-    <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.375" customWidth="1"/>
     <col min="9" max="9" width="19.375" customWidth="1"/>
   </cols>
